--- a/VT_Model_SUP_V01.xlsx
+++ b/VT_Model_SUP_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\bbb\MSc_SELECT-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Nowy folder (17)\MSc_SELECT_ARTUR-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3B79E5-BAF8-41F8-8ADC-A66F838D3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68749BC4-0497-4B92-9B97-73B2F91F1402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEC_Comm" sheetId="112" r:id="rId1"/>
@@ -784,7 +784,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="100">
   <si>
     <t>Define Commodities</t>
   </si>
@@ -1075,6 +1075,15 @@
   </si>
   <si>
     <t>ANNUAL</t>
+  </si>
+  <si>
+    <t>URAN</t>
+  </si>
+  <si>
+    <t>Uranium fuel</t>
+  </si>
+  <si>
+    <t>IMP_URAN</t>
   </si>
 </sst>
 </file>
@@ -3270,10 +3279,22 @@
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="B12" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="F12" s="18"/>
+      <c r="G12" s="23" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="13" spans="2:9">
       <c r="F13" s="18"/>
@@ -3580,6 +3601,23 @@
       </c>
       <c r="I11" s="21"/>
       <c r="J11" s="21"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="23"/>
@@ -3966,6 +4004,17 @@
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:20">
+      <c r="B12" s="28" t="str">
+        <f>SEC_Processes!D12</f>
+        <v>IMP_URAN</v>
+      </c>
+      <c r="D12" t="str">
+        <f>SEC_Comm!C12</f>
+        <v>URAN</v>
+      </c>
+      <c r="E12">
+        <v>0.5</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="H12" s="14"/>
       <c r="I12" s="5"/>
@@ -4054,18 +4103,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4213,18 +4262,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2354E624-82C6-4C58-B5AA-5F4B4FEE1585}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEC55BD-C1AB-47C6-923C-1E0B74C138B9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BEC55BD-C1AB-47C6-923C-1E0B74C138B9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2354E624-82C6-4C58-B5AA-5F4B4FEE1585}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
